--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360914</v>
+        <v>122360919</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565077</v>
+        <v>565074</v>
       </c>
       <c r="R2" t="n">
-        <v>6704748</v>
+        <v>6704682</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
         <v>122360918</v>
       </c>
       <c r="B3" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360919</v>
+        <v>122360920</v>
       </c>
       <c r="B4" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,10 +922,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565074</v>
+        <v>565088</v>
       </c>
       <c r="R4" t="n">
-        <v>6704682</v>
+        <v>6704755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122360920</v>
+        <v>122360914</v>
       </c>
       <c r="B5" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,35 +1012,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565088</v>
+        <v>565077</v>
       </c>
       <c r="R5" t="n">
-        <v>6704755</v>
+        <v>6704748</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360918</v>
+        <v>122360920</v>
       </c>
       <c r="B3" t="n">
         <v>98185</v>
@@ -815,10 +815,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565075</v>
+        <v>565088</v>
       </c>
       <c r="R3" t="n">
-        <v>6704745</v>
+        <v>6704755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360920</v>
+        <v>122360918</v>
       </c>
       <c r="B4" t="n">
         <v>98185</v>
@@ -922,14 +926,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565088</v>
+        <v>565075</v>
       </c>
       <c r="R4" t="n">
-        <v>6704755</v>
+        <v>6704745</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360919</v>
+        <v>122360918</v>
       </c>
       <c r="B2" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565074</v>
+        <v>565075</v>
       </c>
       <c r="R2" t="n">
-        <v>6704682</v>
+        <v>6704745</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360920</v>
+        <v>122360914</v>
       </c>
       <c r="B3" t="n">
-        <v>98185</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,35 +794,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565088</v>
+        <v>565077</v>
       </c>
       <c r="R3" t="n">
-        <v>6704755</v>
+        <v>6704748</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360918</v>
+        <v>122360919</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565075</v>
+        <v>565074</v>
       </c>
       <c r="R4" t="n">
-        <v>6704745</v>
+        <v>6704682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122360914</v>
+        <v>122360920</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>98197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,31 +1008,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565077</v>
+        <v>565088</v>
       </c>
       <c r="R5" t="n">
-        <v>6704748</v>
+        <v>6704755</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360918</v>
+        <v>122360914</v>
       </c>
       <c r="B2" t="n">
-        <v>98197</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565075</v>
+        <v>565077</v>
       </c>
       <c r="R2" t="n">
-        <v>6704745</v>
+        <v>6704748</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360914</v>
+        <v>122360920</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,31 +794,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565077</v>
+        <v>565088</v>
       </c>
       <c r="R3" t="n">
-        <v>6704748</v>
+        <v>6704755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +896,7 @@
         <v>122360919</v>
       </c>
       <c r="B4" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122360920</v>
+        <v>122360918</v>
       </c>
       <c r="B5" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,14 +1033,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565088</v>
+        <v>565075</v>
       </c>
       <c r="R5" t="n">
-        <v>6704755</v>
+        <v>6704745</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100049</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360920</v>
+        <v>122360918</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,11 +795,6 @@
       <c r="E3" t="n">
         <v>220787</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -815,14 +805,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565088</v>
+        <v>565075</v>
       </c>
       <c r="R3" t="n">
-        <v>6704755</v>
+        <v>6704745</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360919</v>
+        <v>122360920</v>
       </c>
       <c r="B4" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,11 +897,6 @@
       <c r="E4" t="n">
         <v>220787</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -926,10 +907,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565074</v>
+        <v>565088</v>
       </c>
       <c r="R4" t="n">
-        <v>6704682</v>
+        <v>6704755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122360918</v>
+        <v>122360919</v>
       </c>
       <c r="B5" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,11 +1003,6 @@
       <c r="E5" t="n">
         <v>220787</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1045,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565075</v>
+        <v>565074</v>
       </c>
       <c r="R5" t="n">
-        <v>6704745</v>
+        <v>6704682</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122360914</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>100049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -780,7 +785,7 @@
         <v>122360918</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,6 +799,11 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -882,7 +892,7 @@
         <v>122360920</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,6 +906,11 @@
       </c>
       <c r="E4" t="n">
         <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -988,7 +1003,7 @@
         <v>122360919</v>
       </c>
       <c r="B5" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,6 +1017,11 @@
       </c>
       <c r="E5" t="n">
         <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>122360918</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>122360920</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>122360919</v>
       </c>
       <c r="B5" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360914</v>
+        <v>122360918</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565077</v>
+        <v>565075</v>
       </c>
       <c r="R2" t="n">
-        <v>6704748</v>
+        <v>6704745</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360918</v>
+        <v>122360920</v>
       </c>
       <c r="B3" t="n">
         <v>98237</v>
@@ -815,10 +815,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565075</v>
+        <v>565088</v>
       </c>
       <c r="R3" t="n">
-        <v>6704745</v>
+        <v>6704755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360920</v>
+        <v>122360919</v>
       </c>
       <c r="B4" t="n">
         <v>98237</v>
@@ -922,14 +926,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565088</v>
+        <v>565074</v>
       </c>
       <c r="R4" t="n">
-        <v>6704755</v>
+        <v>6704682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122360919</v>
+        <v>122360914</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,31 +1012,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565074</v>
+        <v>565077</v>
       </c>
       <c r="R5" t="n">
-        <v>6704682</v>
+        <v>6704748</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360918</v>
+        <v>122360919</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565075</v>
+        <v>565074</v>
       </c>
       <c r="R2" t="n">
-        <v>6704745</v>
+        <v>6704682</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360920</v>
+        <v>122360914</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,35 +794,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565088</v>
+        <v>565077</v>
       </c>
       <c r="R3" t="n">
-        <v>6704755</v>
+        <v>6704748</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360919</v>
+        <v>122360920</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,10 +922,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565074</v>
+        <v>565088</v>
       </c>
       <c r="R4" t="n">
-        <v>6704682</v>
+        <v>6704755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122360914</v>
+        <v>122360918</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,31 +1012,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565077</v>
+        <v>565075</v>
       </c>
       <c r="R5" t="n">
-        <v>6704748</v>
+        <v>6704745</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360919</v>
+        <v>122360914</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565074</v>
+        <v>565077</v>
       </c>
       <c r="R2" t="n">
-        <v>6704682</v>
+        <v>6704748</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360914</v>
+        <v>122360918</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,31 +794,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565077</v>
+        <v>565075</v>
       </c>
       <c r="R3" t="n">
-        <v>6704748</v>
+        <v>6704745</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122360918</v>
+        <v>122360919</v>
       </c>
       <c r="B5" t="n">
         <v>98240</v>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565075</v>
+        <v>565074</v>
       </c>
       <c r="R5" t="n">
-        <v>6704745</v>
+        <v>6704682</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122360914</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360918</v>
+        <v>122360920</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,10 +815,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565075</v>
+        <v>565088</v>
       </c>
       <c r="R3" t="n">
-        <v>6704745</v>
+        <v>6704755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360920</v>
+        <v>122360918</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,14 +926,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565088</v>
+        <v>565075</v>
       </c>
       <c r="R4" t="n">
-        <v>6704755</v>
+        <v>6704745</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1003,7 @@
         <v>122360919</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360914</v>
+        <v>122360920</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565077</v>
+        <v>565088</v>
       </c>
       <c r="R2" t="n">
-        <v>6704748</v>
+        <v>6704755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360920</v>
+        <v>122360919</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,14 +819,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565088</v>
+        <v>565074</v>
       </c>
       <c r="R3" t="n">
-        <v>6704755</v>
+        <v>6704682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360918</v>
+        <v>122360914</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,31 +905,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565075</v>
+        <v>565077</v>
       </c>
       <c r="R4" t="n">
-        <v>6704745</v>
+        <v>6704748</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122360919</v>
+        <v>122360918</v>
       </c>
       <c r="B5" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565074</v>
+        <v>565075</v>
       </c>
       <c r="R5" t="n">
-        <v>6704682</v>
+        <v>6704745</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360920</v>
+        <v>122360914</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565088</v>
+        <v>565077</v>
       </c>
       <c r="R2" t="n">
-        <v>6704755</v>
+        <v>6704748</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360914</v>
+        <v>122360920</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,31 +901,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565077</v>
+        <v>565088</v>
       </c>
       <c r="R4" t="n">
-        <v>6704748</v>
+        <v>6704755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360920</v>
+        <v>122360912</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hans Udd, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565088</v>
+        <v>565053</v>
       </c>
       <c r="R2" t="n">
-        <v>6704755</v>
+        <v>6705003</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,43 +772,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360919</v>
+        <v>122360914</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565074</v>
+        <v>565077</v>
       </c>
       <c r="R3" t="n">
-        <v>6704682</v>
+        <v>6704748</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,12 +877,7 @@
         <v>122360918</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,43 +976,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122360914</v>
+        <v>122360919</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565077</v>
+        <v>565074</v>
       </c>
       <c r="R5" t="n">
-        <v>6704748</v>
+        <v>6704682</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,6 +1075,112 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122360920</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hans Udd, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565088</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6704755</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 451-2025 artfynd.xlsx
+++ b/artfynd/A 451-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122360912</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122360914</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122360918</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122360919</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,8 +1206,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122360920</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>